--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>426</v>
